--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260818.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>30,670,407</t>
+          <t>17,774,128</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>17,774,128</t>
+          <t>30,670,407</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
